--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_64966_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_64966_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7140678097084ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0512b1d31b874ae6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1050.6424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    855.0203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    871.0002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    916.9645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1176.5812</x:v>
+        <x:v>   1153.4025</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_64966_completo.xlsx
+++ b/4992_Cuenca_Pachitea/_raw_reportes_xlsx/IDConfig_64966_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0512b1d31b874ae6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1e899ef49ab6454a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1333.8059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1372.2706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1511.0971</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1832.6437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1289.2494</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    972.4897</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1108.8728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1307.6556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1544.2287</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1372.9880</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1251.4061</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1503.6653</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1555.5915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1919.6510</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1598.5401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2008.0858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2622.1004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1213.5128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1310.4598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1508.0754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1599.0299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1261.8901</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1571.1999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1710.4773</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2402.2965</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1004.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1007.6219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1192.2624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1468.9671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2392.1015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1670.5358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    948.8223</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    845.5153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    922.4735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    963.9999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    991.1838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    853.9507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    836.0461</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    859.2523</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    965.9219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1157.6374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1380.7977</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1157.1226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1311.4686</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1201.6803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1540.0038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>18/08/2026</x:t>
         </x:is>
       </x:c>
